--- a/Excel/Case Study 1 (Pivot Table).xlsx
+++ b/Excel/Case Study 1 (Pivot Table).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Arbor all Folder\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417B419C-B1AC-456B-A6B1-970618636A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59579719-4C1D-4568-87F0-00B14B471D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12336" activeTab="2" xr2:uid="{36E1DAE4-3135-4FDC-9DD0-A3FD0576339A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{36E1DAE4-3135-4FDC-9DD0-A3FD0576339A}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="8" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -684,7 +684,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -734,7 +734,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2539,27 +2538,12 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A5AB3866-D793-4F60-BE28-33D302821C6A}" name="PivotTable36" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C550:H553" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE1C2FED-B5BB-4621-91D0-4F35CE187168}" name="PivotTable23" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C357:D362" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="12">
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="10"/>
-        <item x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="0"/>
-        <item h="1" x="9"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
       <items count="5">
         <item x="3"/>
         <item x="1"/>
@@ -2575,38 +2559,30 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="2"/>
   </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="6"/>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="1" baseItem="0"/>
+    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -2621,75 +2597,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{800323FE-8608-42B0-AC3D-EF77B9EE6EA3}" name="PivotTable14" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C275:E280" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="2" baseItem="0"/>
-    <dataField name="Min of Sales2" fld="5" subtotal="min" baseField="2" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C5C8F70-2E95-4E95-AEF9-F2FD02FDEFCF}" name="PivotTable15" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C5C8F70-2E95-4E95-AEF9-F2FD02FDEFCF}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C284:D286" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -2754,179 +2662,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED4AC1D3-68C8-4D32-9010-BCAC66923498}" name="PivotTable26" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C489:D501" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="12">
-        <item x="6"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7358158-1006-4058-B567-4E7136822401}" name="PivotTable5" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C28:C40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="12">
-        <item x="6"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1F5E572-9F11-4BC4-B160-8D364D5A7654}" name="PivotTable20" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1F5E572-9F11-4BC4-B160-8D364D5A7654}" name="PivotTable20" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C335:O341" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -3037,81 +2774,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09EF4E94-8369-4416-AEAB-35A5B189A28D}" name="PivotTable7" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C130:E133" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="12">
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="10"/>
-        <item x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="0"/>
-        <item h="1" x="9"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D969C134-0D27-4A23-BE7E-8E6E6E9616B0}" name="PivotTable27" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D969C134-0D27-4A23-BE7E-8E6E6E9616B0}" name="PivotTable27" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C387:C467" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -3466,38 +3130,31 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{43E214C9-89DF-457C-8419-52754537F87D}" name="PivotTable19" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C319:D331" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{800323FE-8608-42B0-AC3D-EF77B9EE6EA3}" name="PivotTable14" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C275:E280" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="12">
-        <item x="6"/>
-        <item x="8"/>
+      <items count="5">
         <item x="3"/>
         <item x="1"/>
+        <item x="0"/>
         <item x="2"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="2"/>
   </rowFields>
-  <rowItems count="12">
+  <rowItems count="5">
     <i>
       <x/>
     </i>
@@ -3509,43 +3166,26 @@
     </i>
     <i>
       <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
   </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Sales" fld="5" subtotal="average" baseField="1" baseItem="0" numFmtId="2"/>
+  <dataFields count="2">
+    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="2" baseItem="0"/>
+    <dataField name="Min of Sales2" fld="5" subtotal="min" baseField="2" baseItem="0"/>
   </dataFields>
-  <formats count="1">
-    <format dxfId="0">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3558,12 +3198,27 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96ED699D-960A-4F08-AB87-50792485E0C9}" name="PivotTable22" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C352:C353" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB171EA3-0B8F-4B04-8AD5-5823F2D3A881}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C22:D24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item h="1" x="3"/>
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="10"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="9"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -3571,8 +3226,16 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowItems count="1">
-    <i/>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </rowItems>
   <colItems count="1">
     <i/>
@@ -3592,441 +3255,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1B2E8D4-510A-466F-A052-B71C44FF6039}" name="PivotTable13" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C269:D271" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="80">
-        <item h="1" x="60"/>
-        <item h="1" x="0"/>
-        <item h="1" x="71"/>
-        <item h="1" x="1"/>
-        <item h="1" x="21"/>
-        <item h="1" x="25"/>
-        <item h="1" x="59"/>
-        <item h="1" x="2"/>
-        <item h="1" x="42"/>
-        <item h="1" x="34"/>
-        <item h="1" x="49"/>
-        <item h="1" x="76"/>
-        <item h="1" x="61"/>
-        <item h="1" x="22"/>
-        <item h="1" x="53"/>
-        <item h="1" x="45"/>
-        <item h="1" x="70"/>
-        <item h="1" x="12"/>
-        <item h="1" x="68"/>
-        <item h="1" x="39"/>
-        <item h="1" x="35"/>
-        <item h="1" x="3"/>
-        <item h="1" x="24"/>
-        <item h="1" x="23"/>
-        <item h="1" x="72"/>
-        <item h="1" x="26"/>
-        <item h="1" x="4"/>
-        <item h="1" x="65"/>
-        <item h="1" x="37"/>
-        <item h="1" x="57"/>
-        <item h="1" x="5"/>
-        <item h="1" x="8"/>
-        <item h="1" x="75"/>
-        <item h="1" x="73"/>
-        <item h="1" x="50"/>
-        <item h="1" x="31"/>
-        <item h="1" x="9"/>
-        <item h="1" x="40"/>
-        <item h="1" x="69"/>
-        <item h="1" x="13"/>
-        <item h="1" x="28"/>
-        <item h="1" x="55"/>
-        <item h="1" x="63"/>
-        <item h="1" x="17"/>
-        <item h="1" x="6"/>
-        <item h="1" x="46"/>
-        <item h="1" x="16"/>
-        <item h="1" x="10"/>
-        <item h="1" x="43"/>
-        <item h="1" x="36"/>
-        <item h="1" x="48"/>
-        <item h="1" x="38"/>
-        <item h="1" x="52"/>
-        <item h="1" x="14"/>
-        <item h="1" x="20"/>
-        <item h="1" x="18"/>
-        <item h="1" x="51"/>
-        <item x="32"/>
-        <item h="1" x="7"/>
-        <item h="1" x="66"/>
-        <item h="1" x="11"/>
-        <item h="1" x="74"/>
-        <item h="1" x="41"/>
-        <item h="1" x="67"/>
-        <item h="1" x="29"/>
-        <item h="1" x="15"/>
-        <item h="1" x="62"/>
-        <item h="1" x="19"/>
-        <item h="1" x="47"/>
-        <item h="1" x="64"/>
-        <item h="1" x="58"/>
-        <item h="1" x="30"/>
-        <item h="1" x="44"/>
-        <item h="1" x="78"/>
-        <item h="1" x="27"/>
-        <item h="1" x="33"/>
-        <item h="1" x="56"/>
-        <item h="1" x="54"/>
-        <item h="1" x="77"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="57"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Max of Units" fld="4" subtotal="max" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0BCFBA86-833A-42E4-AF67-938B1C7B1BF2}" name="PivotTable35" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C543:E546" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="80">
-        <item h="1" x="60"/>
-        <item h="1" x="0"/>
-        <item h="1" x="71"/>
-        <item h="1" x="1"/>
-        <item h="1" x="21"/>
-        <item h="1" x="25"/>
-        <item h="1" x="59"/>
-        <item h="1" x="2"/>
-        <item h="1" x="42"/>
-        <item h="1" x="34"/>
-        <item h="1" x="49"/>
-        <item h="1" x="76"/>
-        <item h="1" x="61"/>
-        <item h="1" x="22"/>
-        <item h="1" x="53"/>
-        <item h="1" x="45"/>
-        <item h="1" x="70"/>
-        <item h="1" x="12"/>
-        <item h="1" x="68"/>
-        <item h="1" x="39"/>
-        <item h="1" x="35"/>
-        <item h="1" x="3"/>
-        <item h="1" x="24"/>
-        <item h="1" x="23"/>
-        <item h="1" x="72"/>
-        <item h="1" x="26"/>
-        <item h="1" x="4"/>
-        <item h="1" x="65"/>
-        <item h="1" x="37"/>
-        <item h="1" x="57"/>
-        <item h="1" x="5"/>
-        <item h="1" x="8"/>
-        <item h="1" x="75"/>
-        <item h="1" x="73"/>
-        <item h="1" x="50"/>
-        <item h="1" x="31"/>
-        <item h="1" x="9"/>
-        <item h="1" x="40"/>
-        <item h="1" x="69"/>
-        <item h="1" x="13"/>
-        <item h="1" x="28"/>
-        <item h="1" x="55"/>
-        <item h="1" x="63"/>
-        <item h="1" x="17"/>
-        <item h="1" x="6"/>
-        <item h="1" x="46"/>
-        <item h="1" x="16"/>
-        <item h="1" x="10"/>
-        <item x="43"/>
-        <item h="1" x="36"/>
-        <item h="1" x="48"/>
-        <item h="1" x="38"/>
-        <item h="1" x="52"/>
-        <item h="1" x="14"/>
-        <item h="1" x="20"/>
-        <item h="1" x="18"/>
-        <item h="1" x="51"/>
-        <item h="1" x="32"/>
-        <item h="1" x="7"/>
-        <item h="1" x="66"/>
-        <item h="1" x="11"/>
-        <item h="1" x="74"/>
-        <item h="1" x="41"/>
-        <item h="1" x="67"/>
-        <item h="1" x="29"/>
-        <item h="1" x="15"/>
-        <item h="1" x="62"/>
-        <item h="1" x="19"/>
-        <item h="1" x="47"/>
-        <item h="1" x="64"/>
-        <item h="1" x="58"/>
-        <item h="1" x="30"/>
-        <item h="1" x="44"/>
-        <item h="1" x="78"/>
-        <item h="1" x="27"/>
-        <item h="1" x="33"/>
-        <item h="1" x="56"/>
-        <item h="1" x="54"/>
-        <item h="1" x="77"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="48"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F3F2B6E-D849-42A6-86E6-C2667A796CF6}" name="PivotTable2" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C12:C13" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Sales" fld="5" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="1">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable21.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD38242D-DD8A-48CB-B391-195FEE736A23}" name="PivotTable25" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C371:C383" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="12">
-        <item x="6"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable22.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE17524A-3D61-4EBB-9DD8-45F76B0E1CD8}" name="PivotTable3" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C17:C18" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Max of COGS" fld="7" subtotal="max" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable23.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE1C2FED-B5BB-4621-91D0-4F35CE187168}" name="PivotTable23" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C357:D362" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{955489EE-B678-44B7-B975-F02ABE7A1CF8}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C176:D181" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -4083,161 +3314,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable24.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56860314-B57A-4966-9D9D-A196A766742B}" name="PivotTable24" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C366:C367" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Units" fld="4" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable25.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0183A0C-4EEC-4A65-A7BA-66E8DFCC3D77}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C3:D8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Units" fld="4" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable26.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{955489EE-B678-44B7-B975-F02ABE7A1CF8}" name="PivotTable11" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C176:D181" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable27.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE386ACB-5142-46FE-83D0-531CC8572FA8}" name="PivotTable28" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C471:H484" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED4AC1D3-68C8-4D32-9010-BCAC66923498}" name="PivotTable26" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C489:D501" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
@@ -4256,19 +3335,11 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -4307,643 +3378,6 @@
     </i>
     <i>
       <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable28.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A1BF90E-F2DA-4E7D-8842-03147B14BBE7}" name="PivotTable6" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C44:O125" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="12">
-        <item x="6"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="80">
-        <item x="60"/>
-        <item x="0"/>
-        <item x="71"/>
-        <item x="1"/>
-        <item x="21"/>
-        <item x="25"/>
-        <item x="59"/>
-        <item x="2"/>
-        <item x="42"/>
-        <item x="34"/>
-        <item x="49"/>
-        <item x="76"/>
-        <item x="61"/>
-        <item x="22"/>
-        <item x="53"/>
-        <item x="45"/>
-        <item x="70"/>
-        <item x="12"/>
-        <item x="68"/>
-        <item x="39"/>
-        <item x="35"/>
-        <item x="3"/>
-        <item x="24"/>
-        <item x="23"/>
-        <item x="72"/>
-        <item x="26"/>
-        <item x="4"/>
-        <item x="65"/>
-        <item x="37"/>
-        <item x="57"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="75"/>
-        <item x="73"/>
-        <item x="50"/>
-        <item x="31"/>
-        <item x="9"/>
-        <item x="40"/>
-        <item x="69"/>
-        <item x="13"/>
-        <item x="28"/>
-        <item x="55"/>
-        <item x="63"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="46"/>
-        <item x="16"/>
-        <item x="10"/>
-        <item x="43"/>
-        <item x="36"/>
-        <item x="48"/>
-        <item x="38"/>
-        <item x="52"/>
-        <item x="14"/>
-        <item x="20"/>
-        <item x="18"/>
-        <item x="51"/>
-        <item x="32"/>
-        <item x="7"/>
-        <item x="66"/>
-        <item x="11"/>
-        <item x="74"/>
-        <item x="41"/>
-        <item x="67"/>
-        <item x="29"/>
-        <item x="15"/>
-        <item x="62"/>
-        <item x="19"/>
-        <item x="47"/>
-        <item x="64"/>
-        <item x="58"/>
-        <item x="30"/>
-        <item x="44"/>
-        <item x="78"/>
-        <item x="27"/>
-        <item x="33"/>
-        <item x="56"/>
-        <item x="54"/>
-        <item x="77"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="80">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="36"/>
-    </i>
-    <i>
-      <x v="37"/>
-    </i>
-    <i>
-      <x v="38"/>
-    </i>
-    <i>
-      <x v="39"/>
-    </i>
-    <i>
-      <x v="40"/>
-    </i>
-    <i>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="42"/>
-    </i>
-    <i>
-      <x v="43"/>
-    </i>
-    <i>
-      <x v="44"/>
-    </i>
-    <i>
-      <x v="45"/>
-    </i>
-    <i>
-      <x v="46"/>
-    </i>
-    <i>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="48"/>
-    </i>
-    <i>
-      <x v="49"/>
-    </i>
-    <i>
-      <x v="50"/>
-    </i>
-    <i>
-      <x v="51"/>
-    </i>
-    <i>
-      <x v="52"/>
-    </i>
-    <i>
-      <x v="53"/>
-    </i>
-    <i>
-      <x v="54"/>
-    </i>
-    <i>
-      <x v="55"/>
-    </i>
-    <i>
-      <x v="56"/>
-    </i>
-    <i>
-      <x v="57"/>
-    </i>
-    <i>
-      <x v="58"/>
-    </i>
-    <i>
-      <x v="59"/>
-    </i>
-    <i>
-      <x v="60"/>
-    </i>
-    <i>
-      <x v="61"/>
-    </i>
-    <i>
-      <x v="62"/>
-    </i>
-    <i>
-      <x v="63"/>
-    </i>
-    <i>
-      <x v="64"/>
-    </i>
-    <i>
-      <x v="65"/>
-    </i>
-    <i>
-      <x v="66"/>
-    </i>
-    <i>
-      <x v="67"/>
-    </i>
-    <i>
-      <x v="68"/>
-    </i>
-    <i>
-      <x v="69"/>
-    </i>
-    <i>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="71"/>
-    </i>
-    <i>
-      <x v="72"/>
-    </i>
-    <i>
-      <x v="73"/>
-    </i>
-    <i>
-      <x v="74"/>
-    </i>
-    <i>
-      <x v="75"/>
-    </i>
-    <i>
-      <x v="76"/>
-    </i>
-    <i>
-      <x v="77"/>
-    </i>
-    <i>
-      <x v="78"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Units" fld="4" subtotal="average" baseField="1" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable29.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A5E1A59E-9A8B-45DC-AD75-B3FB6EFA4BAA}" name="PivotTable16" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C290:D292" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="12">
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item x="2"/>
-        <item h="1" x="10"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="0"/>
-        <item h="1" x="9"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B9CEE91-B27C-4012-A2DA-83D46CA278B7}" name="PivotTable34" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C536:E539" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="12">
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="10"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="0"/>
-        <item h="1" x="9"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="2" count="1" selected="0">
-              <x v="3"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="1" baseItem="9"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable30.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB171EA3-0B8F-4B04-8AD5-5823F2D3A881}" name="PivotTable4" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C22:D24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="12">
-        <item h="1" x="6"/>
-        <item h="1" x="8"/>
-        <item h="1" x="3"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="10"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="0"/>
-        <item h="1" x="9"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -4967,178 +3401,75 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable31.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BBEEDFAB-C5C3-422E-8FA2-C5E78B2F1EEC}" name="PivotTable9" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C144:D156" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C067231D-EF4F-4602-B727-9E26B3FCEACD}" name="PivotTable31" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C516:E519" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="12">
-        <item x="6"/>
+        <item h="1" x="6"/>
         <item x="8"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="10"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="9"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
         <item x="0"/>
-        <item x="9"/>
-        <item x="7"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="1"/>
   </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of COGS" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="4">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="3">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="2">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable32.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2B4EAF71-BE3F-46CD-BAFD-A13219FB4856}" name="PivotTable10" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C160:D172" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="12">
-        <item x="6"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -5152,127 +3483,66 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable33.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FC4FFE0-EBB9-4054-94BD-02C110743D80}" name="PivotTable8" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C137:D139" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09EF4E94-8369-4416-AEAB-35A5B189A28D}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C130:E133" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="80">
-        <item h="1" x="60"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="12">
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="10"/>
+        <item x="5"/>
+        <item h="1" x="4"/>
         <item h="1" x="0"/>
-        <item h="1" x="71"/>
-        <item h="1" x="1"/>
-        <item h="1" x="21"/>
-        <item h="1" x="25"/>
-        <item h="1" x="59"/>
-        <item h="1" x="2"/>
-        <item h="1" x="42"/>
-        <item h="1" x="34"/>
-        <item h="1" x="49"/>
-        <item h="1" x="76"/>
-        <item h="1" x="61"/>
-        <item h="1" x="22"/>
-        <item h="1" x="53"/>
-        <item h="1" x="45"/>
-        <item h="1" x="70"/>
-        <item h="1" x="12"/>
-        <item h="1" x="68"/>
-        <item h="1" x="39"/>
-        <item h="1" x="35"/>
-        <item h="1" x="3"/>
-        <item h="1" x="24"/>
-        <item h="1" x="23"/>
-        <item h="1" x="72"/>
-        <item h="1" x="26"/>
-        <item h="1" x="4"/>
-        <item h="1" x="65"/>
-        <item h="1" x="37"/>
-        <item h="1" x="57"/>
-        <item h="1" x="5"/>
-        <item h="1" x="8"/>
-        <item h="1" x="75"/>
-        <item h="1" x="73"/>
-        <item h="1" x="50"/>
-        <item h="1" x="31"/>
         <item h="1" x="9"/>
-        <item h="1" x="40"/>
-        <item h="1" x="69"/>
-        <item h="1" x="13"/>
-        <item h="1" x="28"/>
-        <item h="1" x="55"/>
-        <item h="1" x="63"/>
-        <item h="1" x="17"/>
-        <item h="1" x="6"/>
-        <item h="1" x="46"/>
-        <item h="1" x="16"/>
-        <item h="1" x="10"/>
-        <item h="1" x="43"/>
-        <item h="1" x="36"/>
-        <item h="1" x="48"/>
-        <item h="1" x="38"/>
-        <item h="1" x="52"/>
-        <item h="1" x="14"/>
-        <item h="1" x="20"/>
-        <item h="1" x="18"/>
-        <item h="1" x="51"/>
-        <item x="32"/>
         <item h="1" x="7"/>
-        <item h="1" x="66"/>
-        <item h="1" x="11"/>
-        <item h="1" x="74"/>
-        <item h="1" x="41"/>
-        <item h="1" x="67"/>
-        <item h="1" x="29"/>
-        <item h="1" x="15"/>
-        <item h="1" x="62"/>
-        <item h="1" x="19"/>
-        <item h="1" x="47"/>
-        <item h="1" x="64"/>
-        <item h="1" x="58"/>
-        <item h="1" x="30"/>
-        <item h="1" x="44"/>
-        <item h="1" x="78"/>
-        <item h="1" x="27"/>
-        <item h="1" x="33"/>
-        <item h="1" x="56"/>
-        <item h="1" x="54"/>
-        <item h="1" x="77"/>
         <item t="default"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
     </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="3"/>
+    <field x="2"/>
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="57"/>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
-  <colItems count="1">
-    <i/>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Max of Total Sales" fld="6" subtotal="max" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -5286,279 +3556,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable34.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0A312A55-3E7C-416F-A09E-D73885EA10D2}" name="PivotTable18" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C302:H315" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="12">
-        <item x="6"/>
-        <item x="8"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="1" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable35.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31C3CCBC-F4C9-4D33-9ECC-B8E0C33ADEB1}" name="PivotTable21" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C345:E348" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0" sortType="descending">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="80">
-        <item h="1" x="60"/>
-        <item h="1" x="0"/>
-        <item h="1" x="71"/>
-        <item h="1" x="1"/>
-        <item h="1" x="21"/>
-        <item h="1" x="25"/>
-        <item x="59"/>
-        <item h="1" x="2"/>
-        <item h="1" x="42"/>
-        <item h="1" x="34"/>
-        <item h="1" x="49"/>
-        <item h="1" x="76"/>
-        <item h="1" x="61"/>
-        <item h="1" x="22"/>
-        <item h="1" x="53"/>
-        <item h="1" x="45"/>
-        <item h="1" x="70"/>
-        <item h="1" x="12"/>
-        <item h="1" x="68"/>
-        <item h="1" x="39"/>
-        <item h="1" x="35"/>
-        <item h="1" x="3"/>
-        <item h="1" x="24"/>
-        <item h="1" x="23"/>
-        <item h="1" x="72"/>
-        <item h="1" x="26"/>
-        <item h="1" x="4"/>
-        <item h="1" x="65"/>
-        <item h="1" x="37"/>
-        <item h="1" x="57"/>
-        <item h="1" x="5"/>
-        <item h="1" x="8"/>
-        <item h="1" x="75"/>
-        <item h="1" x="73"/>
-        <item h="1" x="50"/>
-        <item h="1" x="31"/>
-        <item h="1" x="9"/>
-        <item h="1" x="40"/>
-        <item h="1" x="69"/>
-        <item h="1" x="13"/>
-        <item h="1" x="28"/>
-        <item h="1" x="55"/>
-        <item h="1" x="63"/>
-        <item h="1" x="17"/>
-        <item h="1" x="6"/>
-        <item h="1" x="46"/>
-        <item h="1" x="16"/>
-        <item h="1" x="10"/>
-        <item h="1" x="43"/>
-        <item h="1" x="36"/>
-        <item h="1" x="48"/>
-        <item h="1" x="38"/>
-        <item h="1" x="52"/>
-        <item h="1" x="14"/>
-        <item h="1" x="20"/>
-        <item h="1" x="18"/>
-        <item h="1" x="51"/>
-        <item h="1" x="32"/>
-        <item h="1" x="7"/>
-        <item h="1" x="66"/>
-        <item h="1" x="11"/>
-        <item h="1" x="74"/>
-        <item h="1" x="41"/>
-        <item h="1" x="67"/>
-        <item h="1" x="29"/>
-        <item h="1" x="15"/>
-        <item h="1" x="62"/>
-        <item h="1" x="19"/>
-        <item h="1" x="47"/>
-        <item h="1" x="64"/>
-        <item h="1" x="58"/>
-        <item h="1" x="30"/>
-        <item h="1" x="44"/>
-        <item h="1" x="78"/>
-        <item h="1" x="27"/>
-        <item h="1" x="33"/>
-        <item h="1" x="56"/>
-        <item h="1" x="54"/>
-        <item h="1" x="77"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="2" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable36.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7257A2CD-677B-4C61-8ABE-25F314F11E9F}" name="PivotTable12" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7257A2CD-677B-4C61-8ABE-25F314F11E9F}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C185:D265" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -6009,150 +4008,27 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6B50E2B-E3C4-45C9-86D8-F5DD643CA7F9}" name="PivotTable33" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C529:E532" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FE17524A-3D61-4EBB-9DD8-45F76B0E1CD8}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C17:C18" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="80">
-        <item h="1" x="60"/>
-        <item h="1" x="0"/>
-        <item h="1" x="71"/>
-        <item h="1" x="1"/>
-        <item h="1" x="21"/>
-        <item h="1" x="25"/>
-        <item x="59"/>
-        <item h="1" x="2"/>
-        <item h="1" x="42"/>
-        <item h="1" x="34"/>
-        <item h="1" x="49"/>
-        <item h="1" x="76"/>
-        <item h="1" x="61"/>
-        <item h="1" x="22"/>
-        <item h="1" x="53"/>
-        <item h="1" x="45"/>
-        <item h="1" x="70"/>
-        <item h="1" x="12"/>
-        <item h="1" x="68"/>
-        <item h="1" x="39"/>
-        <item h="1" x="35"/>
-        <item h="1" x="3"/>
-        <item h="1" x="24"/>
-        <item h="1" x="23"/>
-        <item h="1" x="72"/>
-        <item h="1" x="26"/>
-        <item h="1" x="4"/>
-        <item h="1" x="65"/>
-        <item h="1" x="37"/>
-        <item h="1" x="57"/>
-        <item h="1" x="5"/>
-        <item h="1" x="8"/>
-        <item h="1" x="75"/>
-        <item h="1" x="73"/>
-        <item h="1" x="50"/>
-        <item x="31"/>
-        <item h="1" x="9"/>
-        <item h="1" x="40"/>
-        <item h="1" x="69"/>
-        <item h="1" x="13"/>
-        <item h="1" x="28"/>
-        <item h="1" x="55"/>
-        <item h="1" x="63"/>
-        <item h="1" x="17"/>
-        <item h="1" x="6"/>
-        <item h="1" x="46"/>
-        <item h="1" x="16"/>
-        <item h="1" x="10"/>
-        <item h="1" x="43"/>
-        <item h="1" x="36"/>
-        <item h="1" x="48"/>
-        <item h="1" x="38"/>
-        <item h="1" x="52"/>
-        <item h="1" x="14"/>
-        <item h="1" x="20"/>
-        <item h="1" x="18"/>
-        <item h="1" x="51"/>
-        <item h="1" x="32"/>
-        <item h="1" x="7"/>
-        <item h="1" x="66"/>
-        <item h="1" x="11"/>
-        <item h="1" x="74"/>
-        <item h="1" x="41"/>
-        <item h="1" x="67"/>
-        <item h="1" x="29"/>
-        <item h="1" x="15"/>
-        <item h="1" x="62"/>
-        <item h="1" x="19"/>
-        <item h="1" x="47"/>
-        <item h="1" x="64"/>
-        <item h="1" x="58"/>
-        <item h="1" x="30"/>
-        <item h="1" x="44"/>
-        <item h="1" x="78"/>
-        <item h="1" x="27"/>
-        <item h="1" x="33"/>
-        <item h="1" x="56"/>
-        <item h="1" x="54"/>
-        <item h="1" x="77"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
   </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
+  <rowItems count="1">
+    <i/>
   </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
+  <colItems count="1">
+    <i/>
   </colItems>
-  <pageFields count="1">
-    <pageField fld="2" hier="-1"/>
-  </pageFields>
-  <dataFields count="2">
-    <dataField name="Min of Sales" fld="5" subtotal="min" baseField="0" baseItem="0"/>
-    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="0" baseItem="1"/>
+  <dataFields count="1">
+    <dataField name="Max of COGS" fld="7" subtotal="max" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -6166,12 +4042,12 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{43B9291F-7406-43C2-A10B-1A2F5CF60EF6}" name="PivotTable32" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C523:E526" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F8112C2-946A-40FB-B1F4-CA08067D24B6}" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C296:D298" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="12">
         <item h="1" x="6"/>
         <item h="1" x="8"/>
@@ -6186,20 +4062,21 @@
         <item h="1" x="7"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
@@ -6213,16 +4090,42 @@
       <x/>
     </i>
   </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable21.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{96ED699D-960A-4F08-AB87-50792485E0C9}" name="PivotTable22" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C352:C353" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
   </colItems>
   <dataFields count="1">
     <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0"/>
@@ -6239,90 +4142,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C067231D-EF4F-4602-B727-9E26B3FCEACD}" name="PivotTable31" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C516:E519" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="12">
-        <item h="1" x="6"/>
-        <item x="8"/>
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="10"/>
-        <item h="1" x="5"/>
-        <item h="1" x="4"/>
-        <item h="1" x="0"/>
-        <item h="1" x="9"/>
-        <item h="1" x="7"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item h="1" x="3"/>
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{200C57F3-9FFD-4C1C-8B22-B0C76D0D501B}" name="PivotTable30" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable22.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{200C57F3-9FFD-4C1C-8B22-B0C76D0D501B}" name="PivotTable30" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C511:C512" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="8">
     <pivotField dataField="1" showAll="0">
@@ -6482,8 +4303,1097 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A5C3E4C-8BFB-4B29-A0B6-20F95F89E2AF}" name="PivotTable29" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable23.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0BCFBA86-833A-42E4-AF67-938B1C7B1BF2}" name="PivotTable35" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C543:E546" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="80">
+        <item h="1" x="60"/>
+        <item h="1" x="0"/>
+        <item h="1" x="71"/>
+        <item h="1" x="1"/>
+        <item h="1" x="21"/>
+        <item h="1" x="25"/>
+        <item h="1" x="59"/>
+        <item h="1" x="2"/>
+        <item h="1" x="42"/>
+        <item h="1" x="34"/>
+        <item h="1" x="49"/>
+        <item h="1" x="76"/>
+        <item h="1" x="61"/>
+        <item h="1" x="22"/>
+        <item h="1" x="53"/>
+        <item h="1" x="45"/>
+        <item h="1" x="70"/>
+        <item h="1" x="12"/>
+        <item h="1" x="68"/>
+        <item h="1" x="39"/>
+        <item h="1" x="35"/>
+        <item h="1" x="3"/>
+        <item h="1" x="24"/>
+        <item h="1" x="23"/>
+        <item h="1" x="72"/>
+        <item h="1" x="26"/>
+        <item h="1" x="4"/>
+        <item h="1" x="65"/>
+        <item h="1" x="37"/>
+        <item h="1" x="57"/>
+        <item h="1" x="5"/>
+        <item h="1" x="8"/>
+        <item h="1" x="75"/>
+        <item h="1" x="73"/>
+        <item h="1" x="50"/>
+        <item h="1" x="31"/>
+        <item h="1" x="9"/>
+        <item h="1" x="40"/>
+        <item h="1" x="69"/>
+        <item h="1" x="13"/>
+        <item h="1" x="28"/>
+        <item h="1" x="55"/>
+        <item h="1" x="63"/>
+        <item h="1" x="17"/>
+        <item h="1" x="6"/>
+        <item h="1" x="46"/>
+        <item h="1" x="16"/>
+        <item h="1" x="10"/>
+        <item x="43"/>
+        <item h="1" x="36"/>
+        <item h="1" x="48"/>
+        <item h="1" x="38"/>
+        <item h="1" x="52"/>
+        <item h="1" x="14"/>
+        <item h="1" x="20"/>
+        <item h="1" x="18"/>
+        <item h="1" x="51"/>
+        <item h="1" x="32"/>
+        <item h="1" x="7"/>
+        <item h="1" x="66"/>
+        <item h="1" x="11"/>
+        <item h="1" x="74"/>
+        <item h="1" x="41"/>
+        <item h="1" x="67"/>
+        <item h="1" x="29"/>
+        <item h="1" x="15"/>
+        <item h="1" x="62"/>
+        <item h="1" x="19"/>
+        <item h="1" x="47"/>
+        <item h="1" x="64"/>
+        <item h="1" x="58"/>
+        <item h="1" x="30"/>
+        <item h="1" x="44"/>
+        <item h="1" x="78"/>
+        <item h="1" x="27"/>
+        <item h="1" x="33"/>
+        <item h="1" x="56"/>
+        <item h="1" x="54"/>
+        <item h="1" x="77"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="48"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable24.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{43B9291F-7406-43C2-A10B-1A2F5CF60EF6}" name="PivotTable32" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C523:E526" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="10"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
+        <item x="0"/>
+        <item h="1" x="9"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Sales" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable25.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EE386ACB-5142-46FE-83D0-531CC8572FA8}" name="PivotTable28" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C471:H484" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item x="6"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable26.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0A312A55-3E7C-416F-A09E-D73885EA10D2}" name="PivotTable18" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C302:H315" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item x="6"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable27.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A5AB3866-D793-4F60-BE28-33D302821C6A}" name="PivotTable36" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C550:H553" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="10"/>
+        <item x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="9"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable28.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A1BF90E-F2DA-4E7D-8842-03147B14BBE7}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C44:O125" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="12">
+        <item x="6"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="80">
+        <item x="60"/>
+        <item x="0"/>
+        <item x="71"/>
+        <item x="1"/>
+        <item x="21"/>
+        <item x="25"/>
+        <item x="59"/>
+        <item x="2"/>
+        <item x="42"/>
+        <item x="34"/>
+        <item x="49"/>
+        <item x="76"/>
+        <item x="61"/>
+        <item x="22"/>
+        <item x="53"/>
+        <item x="45"/>
+        <item x="70"/>
+        <item x="12"/>
+        <item x="68"/>
+        <item x="39"/>
+        <item x="35"/>
+        <item x="3"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="72"/>
+        <item x="26"/>
+        <item x="4"/>
+        <item x="65"/>
+        <item x="37"/>
+        <item x="57"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="75"/>
+        <item x="73"/>
+        <item x="50"/>
+        <item x="31"/>
+        <item x="9"/>
+        <item x="40"/>
+        <item x="69"/>
+        <item x="13"/>
+        <item x="28"/>
+        <item x="55"/>
+        <item x="63"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="46"/>
+        <item x="16"/>
+        <item x="10"/>
+        <item x="43"/>
+        <item x="36"/>
+        <item x="48"/>
+        <item x="38"/>
+        <item x="52"/>
+        <item x="14"/>
+        <item x="20"/>
+        <item x="18"/>
+        <item x="51"/>
+        <item x="32"/>
+        <item x="7"/>
+        <item x="66"/>
+        <item x="11"/>
+        <item x="74"/>
+        <item x="41"/>
+        <item x="67"/>
+        <item x="29"/>
+        <item x="15"/>
+        <item x="62"/>
+        <item x="19"/>
+        <item x="47"/>
+        <item x="64"/>
+        <item x="58"/>
+        <item x="30"/>
+        <item x="44"/>
+        <item x="78"/>
+        <item x="27"/>
+        <item x="33"/>
+        <item x="56"/>
+        <item x="54"/>
+        <item x="77"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="80">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="59"/>
+    </i>
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="62"/>
+    </i>
+    <i>
+      <x v="63"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i>
+      <x v="65"/>
+    </i>
+    <i>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="67"/>
+    </i>
+    <i>
+      <x v="68"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="71"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="75"/>
+    </i>
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="77"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Units" fld="4" subtotal="average" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable29.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6B50E2B-E3C4-45C9-86D8-F5DD643CA7F9}" name="PivotTable33" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C529:E532" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="80">
+        <item h="1" x="60"/>
+        <item h="1" x="0"/>
+        <item h="1" x="71"/>
+        <item h="1" x="1"/>
+        <item h="1" x="21"/>
+        <item h="1" x="25"/>
+        <item x="59"/>
+        <item h="1" x="2"/>
+        <item h="1" x="42"/>
+        <item h="1" x="34"/>
+        <item h="1" x="49"/>
+        <item h="1" x="76"/>
+        <item h="1" x="61"/>
+        <item h="1" x="22"/>
+        <item h="1" x="53"/>
+        <item h="1" x="45"/>
+        <item h="1" x="70"/>
+        <item h="1" x="12"/>
+        <item h="1" x="68"/>
+        <item h="1" x="39"/>
+        <item h="1" x="35"/>
+        <item h="1" x="3"/>
+        <item h="1" x="24"/>
+        <item h="1" x="23"/>
+        <item h="1" x="72"/>
+        <item h="1" x="26"/>
+        <item h="1" x="4"/>
+        <item h="1" x="65"/>
+        <item h="1" x="37"/>
+        <item h="1" x="57"/>
+        <item h="1" x="5"/>
+        <item h="1" x="8"/>
+        <item h="1" x="75"/>
+        <item h="1" x="73"/>
+        <item h="1" x="50"/>
+        <item x="31"/>
+        <item h="1" x="9"/>
+        <item h="1" x="40"/>
+        <item h="1" x="69"/>
+        <item h="1" x="13"/>
+        <item h="1" x="28"/>
+        <item h="1" x="55"/>
+        <item h="1" x="63"/>
+        <item h="1" x="17"/>
+        <item h="1" x="6"/>
+        <item h="1" x="46"/>
+        <item h="1" x="16"/>
+        <item h="1" x="10"/>
+        <item h="1" x="43"/>
+        <item h="1" x="36"/>
+        <item h="1" x="48"/>
+        <item h="1" x="38"/>
+        <item h="1" x="52"/>
+        <item h="1" x="14"/>
+        <item h="1" x="20"/>
+        <item h="1" x="18"/>
+        <item h="1" x="51"/>
+        <item h="1" x="32"/>
+        <item h="1" x="7"/>
+        <item h="1" x="66"/>
+        <item h="1" x="11"/>
+        <item h="1" x="74"/>
+        <item h="1" x="41"/>
+        <item h="1" x="67"/>
+        <item h="1" x="29"/>
+        <item h="1" x="15"/>
+        <item h="1" x="62"/>
+        <item h="1" x="19"/>
+        <item h="1" x="47"/>
+        <item h="1" x="64"/>
+        <item h="1" x="58"/>
+        <item h="1" x="30"/>
+        <item h="1" x="44"/>
+        <item h="1" x="78"/>
+        <item h="1" x="27"/>
+        <item h="1" x="33"/>
+        <item h="1" x="56"/>
+        <item h="1" x="54"/>
+        <item h="1" x="77"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="2">
+    <dataField name="Min of Sales" fld="5" subtotal="min" baseField="0" baseItem="0"/>
+    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="0" baseItem="1"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7A5C3E4C-8BFB-4B29-A0B6-20F95F89E2AF}" name="PivotTable29" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="C505:D507" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -6616,22 +5526,568 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0F8112C2-946A-40FB-B1F4-CA08067D24B6}" name="PivotTable17" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C296:D298" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable30.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7358158-1006-4058-B567-4E7136822401}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C28:C40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item x="6"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable31.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FC4FFE0-EBB9-4054-94BD-02C110743D80}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C137:D139" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="80">
+        <item h="1" x="60"/>
+        <item h="1" x="0"/>
+        <item h="1" x="71"/>
+        <item h="1" x="1"/>
+        <item h="1" x="21"/>
+        <item h="1" x="25"/>
+        <item h="1" x="59"/>
+        <item h="1" x="2"/>
+        <item h="1" x="42"/>
+        <item h="1" x="34"/>
+        <item h="1" x="49"/>
+        <item h="1" x="76"/>
+        <item h="1" x="61"/>
+        <item h="1" x="22"/>
+        <item h="1" x="53"/>
+        <item h="1" x="45"/>
+        <item h="1" x="70"/>
+        <item h="1" x="12"/>
+        <item h="1" x="68"/>
+        <item h="1" x="39"/>
+        <item h="1" x="35"/>
+        <item h="1" x="3"/>
+        <item h="1" x="24"/>
+        <item h="1" x="23"/>
+        <item h="1" x="72"/>
+        <item h="1" x="26"/>
+        <item h="1" x="4"/>
+        <item h="1" x="65"/>
+        <item h="1" x="37"/>
+        <item h="1" x="57"/>
+        <item h="1" x="5"/>
+        <item h="1" x="8"/>
+        <item h="1" x="75"/>
+        <item h="1" x="73"/>
+        <item h="1" x="50"/>
+        <item h="1" x="31"/>
+        <item h="1" x="9"/>
+        <item h="1" x="40"/>
+        <item h="1" x="69"/>
+        <item h="1" x="13"/>
+        <item h="1" x="28"/>
+        <item h="1" x="55"/>
+        <item h="1" x="63"/>
+        <item h="1" x="17"/>
+        <item h="1" x="6"/>
+        <item h="1" x="46"/>
+        <item h="1" x="16"/>
+        <item h="1" x="10"/>
+        <item h="1" x="43"/>
+        <item h="1" x="36"/>
+        <item h="1" x="48"/>
+        <item h="1" x="38"/>
+        <item h="1" x="52"/>
+        <item h="1" x="14"/>
+        <item h="1" x="20"/>
+        <item h="1" x="18"/>
+        <item h="1" x="51"/>
+        <item x="32"/>
+        <item h="1" x="7"/>
+        <item h="1" x="66"/>
+        <item h="1" x="11"/>
+        <item h="1" x="74"/>
+        <item h="1" x="41"/>
+        <item h="1" x="67"/>
+        <item h="1" x="29"/>
+        <item h="1" x="15"/>
+        <item h="1" x="62"/>
+        <item h="1" x="19"/>
+        <item h="1" x="47"/>
+        <item h="1" x="64"/>
+        <item h="1" x="58"/>
+        <item h="1" x="30"/>
+        <item h="1" x="44"/>
+        <item h="1" x="78"/>
+        <item h="1" x="27"/>
+        <item h="1" x="33"/>
+        <item h="1" x="56"/>
+        <item h="1" x="54"/>
+        <item h="1" x="77"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="57"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Total Sales" fld="6" subtotal="max" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable32.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2B4EAF71-BE3F-46CD-BAFD-A13219FB4856}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C160:D172" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item x="6"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable33.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BBEEDFAB-C5C3-422E-8FA2-C5E78B2F1EEC}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C144:D156" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item x="6"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of COGS" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="4">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable34.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CD38242D-DD8A-48CB-B391-195FEE736A23}" name="PivotTable25" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C371:C383" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item x="6"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable35.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0183A0C-4EEC-4A65-A7BA-66E8DFCC3D77}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C3:D8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable36.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A5E1A59E-9A8B-45DC-AD75-B3FB6EFA4BAA}" name="PivotTable16" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C290:D292" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="12">
         <item h="1" x="6"/>
         <item h="1" x="8"/>
         <item h="1" x="3"/>
         <item h="1" x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item h="1" x="10"/>
         <item h="1" x="5"/>
         <item h="1" x="4"/>
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item h="1" x="9"/>
         <item h="1" x="7"/>
         <item t="default"/>
@@ -6658,7 +6114,7 @@
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="8"/>
+      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -6670,6 +6126,549 @@
   <dataFields count="1">
     <dataField name="Sum of Sales" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9F3F2B6E-D849-42A6-86E6-C2667A796CF6}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C12:C13" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Sales" fld="5" subtotal="average" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="0">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56860314-B57A-4966-9D9D-A196A766742B}" name="PivotTable24" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C366:C367" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Units" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1B2E8D4-510A-466F-A052-B71C44FF6039}" name="PivotTable13" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C269:D271" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="80">
+        <item h="1" x="60"/>
+        <item h="1" x="0"/>
+        <item h="1" x="71"/>
+        <item h="1" x="1"/>
+        <item h="1" x="21"/>
+        <item h="1" x="25"/>
+        <item h="1" x="59"/>
+        <item h="1" x="2"/>
+        <item h="1" x="42"/>
+        <item h="1" x="34"/>
+        <item h="1" x="49"/>
+        <item h="1" x="76"/>
+        <item h="1" x="61"/>
+        <item h="1" x="22"/>
+        <item h="1" x="53"/>
+        <item h="1" x="45"/>
+        <item h="1" x="70"/>
+        <item h="1" x="12"/>
+        <item h="1" x="68"/>
+        <item h="1" x="39"/>
+        <item h="1" x="35"/>
+        <item h="1" x="3"/>
+        <item h="1" x="24"/>
+        <item h="1" x="23"/>
+        <item h="1" x="72"/>
+        <item h="1" x="26"/>
+        <item h="1" x="4"/>
+        <item h="1" x="65"/>
+        <item h="1" x="37"/>
+        <item h="1" x="57"/>
+        <item h="1" x="5"/>
+        <item h="1" x="8"/>
+        <item h="1" x="75"/>
+        <item h="1" x="73"/>
+        <item h="1" x="50"/>
+        <item h="1" x="31"/>
+        <item h="1" x="9"/>
+        <item h="1" x="40"/>
+        <item h="1" x="69"/>
+        <item h="1" x="13"/>
+        <item h="1" x="28"/>
+        <item h="1" x="55"/>
+        <item h="1" x="63"/>
+        <item h="1" x="17"/>
+        <item h="1" x="6"/>
+        <item h="1" x="46"/>
+        <item h="1" x="16"/>
+        <item h="1" x="10"/>
+        <item h="1" x="43"/>
+        <item h="1" x="36"/>
+        <item h="1" x="48"/>
+        <item h="1" x="38"/>
+        <item h="1" x="52"/>
+        <item h="1" x="14"/>
+        <item h="1" x="20"/>
+        <item h="1" x="18"/>
+        <item h="1" x="51"/>
+        <item x="32"/>
+        <item h="1" x="7"/>
+        <item h="1" x="66"/>
+        <item h="1" x="11"/>
+        <item h="1" x="74"/>
+        <item h="1" x="41"/>
+        <item h="1" x="67"/>
+        <item h="1" x="29"/>
+        <item h="1" x="15"/>
+        <item h="1" x="62"/>
+        <item h="1" x="19"/>
+        <item h="1" x="47"/>
+        <item h="1" x="64"/>
+        <item h="1" x="58"/>
+        <item h="1" x="30"/>
+        <item h="1" x="44"/>
+        <item h="1" x="78"/>
+        <item h="1" x="27"/>
+        <item h="1" x="33"/>
+        <item h="1" x="56"/>
+        <item h="1" x="54"/>
+        <item h="1" x="77"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="57"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Units" fld="4" subtotal="max" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{31C3CCBC-F4C9-4D33-9ECC-B8E0C33ADEB1}" name="PivotTable21" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C345:E348" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0" sortType="descending">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="80">
+        <item h="1" x="60"/>
+        <item h="1" x="0"/>
+        <item h="1" x="71"/>
+        <item h="1" x="1"/>
+        <item h="1" x="21"/>
+        <item h="1" x="25"/>
+        <item x="59"/>
+        <item h="1" x="2"/>
+        <item h="1" x="42"/>
+        <item h="1" x="34"/>
+        <item h="1" x="49"/>
+        <item h="1" x="76"/>
+        <item h="1" x="61"/>
+        <item h="1" x="22"/>
+        <item h="1" x="53"/>
+        <item h="1" x="45"/>
+        <item h="1" x="70"/>
+        <item h="1" x="12"/>
+        <item h="1" x="68"/>
+        <item h="1" x="39"/>
+        <item h="1" x="35"/>
+        <item h="1" x="3"/>
+        <item h="1" x="24"/>
+        <item h="1" x="23"/>
+        <item h="1" x="72"/>
+        <item h="1" x="26"/>
+        <item h="1" x="4"/>
+        <item h="1" x="65"/>
+        <item h="1" x="37"/>
+        <item h="1" x="57"/>
+        <item h="1" x="5"/>
+        <item h="1" x="8"/>
+        <item h="1" x="75"/>
+        <item h="1" x="73"/>
+        <item h="1" x="50"/>
+        <item h="1" x="31"/>
+        <item h="1" x="9"/>
+        <item h="1" x="40"/>
+        <item h="1" x="69"/>
+        <item h="1" x="13"/>
+        <item h="1" x="28"/>
+        <item h="1" x="55"/>
+        <item h="1" x="63"/>
+        <item h="1" x="17"/>
+        <item h="1" x="6"/>
+        <item h="1" x="46"/>
+        <item h="1" x="16"/>
+        <item h="1" x="10"/>
+        <item h="1" x="43"/>
+        <item h="1" x="36"/>
+        <item h="1" x="48"/>
+        <item h="1" x="38"/>
+        <item h="1" x="52"/>
+        <item h="1" x="14"/>
+        <item h="1" x="20"/>
+        <item h="1" x="18"/>
+        <item h="1" x="51"/>
+        <item h="1" x="32"/>
+        <item h="1" x="7"/>
+        <item h="1" x="66"/>
+        <item h="1" x="11"/>
+        <item h="1" x="74"/>
+        <item h="1" x="41"/>
+        <item h="1" x="67"/>
+        <item h="1" x="29"/>
+        <item h="1" x="15"/>
+        <item h="1" x="62"/>
+        <item h="1" x="19"/>
+        <item h="1" x="47"/>
+        <item h="1" x="64"/>
+        <item h="1" x="58"/>
+        <item h="1" x="30"/>
+        <item h="1" x="44"/>
+        <item h="1" x="78"/>
+        <item h="1" x="27"/>
+        <item h="1" x="33"/>
+        <item h="1" x="56"/>
+        <item h="1" x="54"/>
+        <item h="1" x="77"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="2" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B9CEE91-B27C-4012-A2DA-83D46CA278B7}" name="PivotTable34" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C536:E539" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="12">
+        <item h="1" x="6"/>
+        <item h="1" x="8"/>
+        <item x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="10"/>
+        <item h="1" x="5"/>
+        <item h="1" x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="9"/>
+        <item h="1" x="7"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="2" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item h="1" x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Max of Sales" fld="5" subtotal="max" baseField="1" baseItem="9"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{43E214C9-89DF-457C-8419-52754537F87D}" name="PivotTable19" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C319:D331" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="12">
+        <item x="6"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Sales" fld="5" subtotal="average" baseField="1" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="1">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -14952,7 +14951,7 @@
       </c>
     </row>
     <row r="512" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C512" s="19">
+      <c r="C512">
         <v>123</v>
       </c>
     </row>
@@ -14987,10 +14986,10 @@
       <c r="C518" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D518" s="19">
+      <c r="D518">
         <v>988</v>
       </c>
-      <c r="E518" s="19">
+      <c r="E518">
         <v>988</v>
       </c>
     </row>
@@ -14998,10 +14997,10 @@
       <c r="C519" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D519" s="19">
+      <c r="D519">
         <v>988</v>
       </c>
-      <c r="E519" s="19">
+      <c r="E519">
         <v>988</v>
       </c>
     </row>
@@ -15036,10 +15035,10 @@
       <c r="C525" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D525" s="19">
+      <c r="D525">
         <v>51135</v>
       </c>
-      <c r="E525" s="19">
+      <c r="E525">
         <v>51135</v>
       </c>
     </row>
@@ -15047,10 +15046,10 @@
       <c r="C526" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D526" s="19">
+      <c r="D526">
         <v>51135</v>
       </c>
-      <c r="E526" s="19">
+      <c r="E526">
         <v>51135</v>
       </c>
     </row>
@@ -15085,10 +15084,10 @@
       <c r="C530" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D530" s="19">
+      <c r="D530">
         <v>125</v>
       </c>
-      <c r="E530" s="19">
+      <c r="E530">
         <v>265</v>
       </c>
     </row>
@@ -15096,10 +15095,10 @@
       <c r="C531" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D531" s="19">
+      <c r="D531">
         <v>765</v>
       </c>
-      <c r="E531" s="19">
+      <c r="E531">
         <v>988</v>
       </c>
     </row>
@@ -15107,10 +15106,10 @@
       <c r="C532" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D532" s="19">
+      <c r="D532">
         <v>125</v>
       </c>
-      <c r="E532" s="19">
+      <c r="E532">
         <v>988</v>
       </c>
     </row>
@@ -15145,10 +15144,10 @@
       <c r="C538" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D538" s="19">
+      <c r="D538">
         <v>999</v>
       </c>
-      <c r="E538" s="19">
+      <c r="E538">
         <v>999</v>
       </c>
     </row>
@@ -15156,10 +15155,10 @@
       <c r="C539" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D539" s="19">
+      <c r="D539">
         <v>999</v>
       </c>
-      <c r="E539" s="19">
+      <c r="E539">
         <v>999</v>
       </c>
     </row>
@@ -15194,10 +15193,10 @@
       <c r="C545" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D545" s="19">
+      <c r="D545">
         <v>12432</v>
       </c>
-      <c r="E545" s="19">
+      <c r="E545">
         <v>12432</v>
       </c>
     </row>
@@ -15205,10 +15204,10 @@
       <c r="C546" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D546" s="19">
+      <c r="D546">
         <v>12432</v>
       </c>
-      <c r="E546" s="19">
+      <c r="E546">
         <v>12432</v>
       </c>
     </row>
@@ -15252,19 +15251,19 @@
       <c r="C552" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D552" s="19">
+      <c r="D552">
         <v>999</v>
       </c>
-      <c r="E552" s="19">
+      <c r="E552">
         <v>777</v>
       </c>
-      <c r="F552" s="19">
+      <c r="F552">
         <v>699</v>
       </c>
-      <c r="G552" s="19">
+      <c r="G552">
         <v>223</v>
       </c>
-      <c r="H552" s="19">
+      <c r="H552">
         <v>999</v>
       </c>
     </row>
@@ -15272,19 +15271,19 @@
       <c r="C553" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D553" s="19">
+      <c r="D553">
         <v>999</v>
       </c>
-      <c r="E553" s="19">
+      <c r="E553">
         <v>777</v>
       </c>
-      <c r="F553" s="19">
+      <c r="F553">
         <v>699</v>
       </c>
-      <c r="G553" s="19">
+      <c r="G553">
         <v>223</v>
       </c>
-      <c r="H553" s="19">
+      <c r="H553">
         <v>999</v>
       </c>
     </row>
